--- a/questionnaire_templates/028_course_creator_readiness_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/028_course_creator_readiness_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>course_creator_readiness_assessment</t>
+          <t>How ready are you to create an online course?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marketing_strategy</t>
+          <t>What is your marketing strategy for the course?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>course_creator_experience</t>
+          <t>Describe your experience in creating online courses.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>Who is your target audience for the course?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>course_creation_process</t>
+          <t>What is the process of creating an online course?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,82 +640,82 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>course_launch_strategy</t>
+          <t>What is your course launch strategy?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>course_creation_process</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>course_creation_process</t>
+          <t>What type of content do you plan to create for the course (video, text, images, audio, assessments)?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>course_launch_strategy</t>
+          <t>target_audience_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>course_launch_strategy</t>
+          <t>Target Audience 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>content</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>Describe your course content creation process.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,62 +727,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>course_creation_process</t>
+          <t>launch_strategy_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>course_creation_process</t>
+          <t>How will you launch your course?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>course_launch_strategy</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>course_launch_strategy</t>
+          <t>Additional notes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>target_audience</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>target_audience</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>how_ready_are_you_to_create_an_online_course?</t>
+          <t>very_ready</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>How ready are you to create an online course?</t>
+          <t>Very ready</t>
         </is>
       </c>
     </row>
@@ -849,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_at_all_ready</t>
+          <t>somewhat_ready</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Not at all ready</t>
+          <t>Somewhat ready</t>
         </is>
       </c>
     </row>
@@ -866,29 +843,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>somewhat_ready</t>
+          <t>not_at_all_ready</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Somewhat ready</t>
+          <t>Not at all ready</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>course_creator_readiness_assessment_1_choices</t>
+          <t>target_audience_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>very_ready</t>
+          <t>students</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Very ready</t>
+          <t>Students</t>
         </is>
       </c>
     </row>
@@ -900,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>coaches</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Coaches</t>
         </is>
       </c>
     </row>
@@ -917,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>coaches</t>
+          <t>trainers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coaches</t>
+          <t>Trainers</t>
         </is>
       </c>
     </row>
@@ -934,420 +911,199 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>trainers</t>
+          <t>educators</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trainers</t>
+          <t>Educators</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>course_launch_strategy_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>educators</t>
+          <t>launch_in_phases</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Educators</t>
+          <t>Launch in phases</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>course_launch_strategy_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>coaches_and_trainers</t>
+          <t>launch_all_at_once</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coaches and trainers</t>
+          <t>Launch all at once</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trainers_and_educators</t>
+          <t>video_content</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trainers and educators</t>
+          <t>Video content</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>course_creation_process_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>creating_an_online_course_involves_creating_high_quality_video_content</t>
+          <t>text_content</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Creating an online course involves creating high quality video content</t>
+          <t>Text content</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>course_creation_process_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>creating_an_online_course_involves_creating_high_quality_text_content</t>
+          <t>image_content</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Creating an online course involves creating high quality text content</t>
+          <t>Image content</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>course_creation_process_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>creating_an_online_course_involves_creating_high_quality_images</t>
+          <t>audio_content</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Creating an online course involves creating high quality images</t>
+          <t>Audio content</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>course_creation_process_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>creating_an_online_course_involves_creating_high_quality_audio_content</t>
+          <t>assessment_content</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Creating an online course involves creating high quality audio content</t>
+          <t>Assessment content</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>course_creation_process_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>creating_an_online_course_involves_creating_high_quality_assessments</t>
+          <t>students</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Creating an online course involves creating high quality assessments</t>
+          <t>Students</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>course_creation_process_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>coaches</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Coaches</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>course_launch_strategy_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>launch_in_phases</t>
+          <t>trainers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Launch in phases</t>
+          <t>Trainers</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>course_launch_strategy_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>launch_all_at_once</t>
+          <t>educators</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Launch all at once</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>course_launch_strategy_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>coaches</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Coaches</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>trainers</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Trainers</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>educators</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>Educators</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>coaches_and_trainers</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Coaches and trainers</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>trainers_and_educators</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Trainers and educators</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>coaches</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Coaches</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>trainers</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Trainers</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>educators</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Educators</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>coaches_and_trainers</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Coaches and trainers</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>trainers_and_educators</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Trainers and educators</t>
         </is>
       </c>
     </row>
